--- a/HOSPITALITY MEMBERS.xlsx
+++ b/HOSPITALITY MEMBERS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/341706f11dbb6ad1/Documents/Protocol Bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{B8933D2A-CF6E-47BB-B1FC-6E30EEB082BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DBC35F2-04F7-4B39-A1EB-4D46B7D7FF82}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{B8933D2A-CF6E-47BB-B1FC-6E30EEB082BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF83D1CF-B224-476B-9B87-37EDF33BBBA7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{4C2305D9-A961-4A00-AA72-500382EFDABF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="157">
   <si>
     <t>NAME</t>
   </si>
@@ -420,9 +420,6 @@
     <t>@xster_xo</t>
   </si>
   <si>
-    <t>@e_nexoxo</t>
-  </si>
-  <si>
     <t>@T1m0thy_le0</t>
   </si>
   <si>
@@ -469,6 +466,45 @@
   </si>
   <si>
     <t>TELEGRAM_HANDLE</t>
+  </si>
+  <si>
+    <t>@Tio_luwa</t>
+  </si>
+  <si>
+    <t>@Ugochiiiiiiiii</t>
+  </si>
+  <si>
+    <t>@Vee_ge0rge</t>
+  </si>
+  <si>
+    <t>@ebere_ifeanyi</t>
+  </si>
+  <si>
+    <t>@toluwanibode</t>
+  </si>
+  <si>
+    <t>@ikenna_amarachi</t>
+  </si>
+  <si>
+    <t>@Phavourii</t>
+  </si>
+  <si>
+    <t>@Oluwaseyi_esther</t>
+  </si>
+  <si>
+    <t>@Ijetta</t>
+  </si>
+  <si>
+    <t>@tiffanyih</t>
+  </si>
+  <si>
+    <t>@Onaopemipo_Susan</t>
+  </si>
+  <si>
+    <t>@jummyyy</t>
+  </si>
+  <si>
+    <t>@Joyifeee</t>
   </si>
 </sst>
 </file>
@@ -871,12 +907,12 @@
         <v>124</v>
       </c>
       <c r="H1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -902,7 +938,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -922,7 +958,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -942,10 +978,13 @@
       <c r="G4">
         <v>6648354234</v>
       </c>
+      <c r="H4" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -965,10 +1004,13 @@
       <c r="G5">
         <v>5767207003</v>
       </c>
+      <c r="H5" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s">
         <v>8</v>
@@ -988,10 +1030,13 @@
       <c r="G6">
         <v>6478487834</v>
       </c>
+      <c r="H6" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -1011,7 +1056,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B8" t="s">
         <v>8</v>
@@ -1028,10 +1073,16 @@
       <c r="F8" s="1" t="s">
         <v>108</v>
       </c>
+      <c r="G8" s="3">
+        <v>8173599381</v>
+      </c>
+      <c r="H8" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
@@ -1047,6 +1098,12 @@
       </c>
       <c r="F9" s="1" t="s">
         <v>109</v>
+      </c>
+      <c r="G9">
+        <v>2091974524</v>
+      </c>
+      <c r="H9" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1077,7 +1134,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -1097,7 +1154,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -1113,6 +1170,12 @@
       </c>
       <c r="F12" s="1" t="s">
         <v>112</v>
+      </c>
+      <c r="G12" s="3">
+        <v>6663493627</v>
+      </c>
+      <c r="H12" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1134,9 +1197,6 @@
       <c r="F13" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H13" t="s">
-        <v>128</v>
-      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
@@ -1161,7 +1221,7 @@
         <v>6061962761</v>
       </c>
       <c r="H14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1183,6 +1243,12 @@
       <c r="F15" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="G15" s="3">
+        <v>6801992874</v>
+      </c>
+      <c r="H15" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
@@ -1203,6 +1269,12 @@
       <c r="F16" s="1" t="s">
         <v>116</v>
       </c>
+      <c r="G16" s="3">
+        <v>6608140183</v>
+      </c>
+      <c r="H16" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
@@ -1223,6 +1295,12 @@
       <c r="F17" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="G17" s="3">
+        <v>2038382237</v>
+      </c>
+      <c r="H17" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
@@ -1247,7 +1325,7 @@
         <v>6044449971</v>
       </c>
       <c r="H18" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1387,7 +1465,7 @@
         <v>5439664544</v>
       </c>
       <c r="H25" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1684,6 +1762,12 @@
       <c r="E42" t="s">
         <v>92</v>
       </c>
+      <c r="G42" s="3">
+        <v>6178989826</v>
+      </c>
+      <c r="H42" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
@@ -1752,6 +1836,12 @@
       <c r="E46" t="s">
         <v>92</v>
       </c>
+      <c r="G46" s="3">
+        <v>5580932541</v>
+      </c>
+      <c r="H46" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
@@ -1773,7 +1863,7 @@
         <v>6235898696</v>
       </c>
       <c r="H47" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1864,7 +1954,7 @@
         <v>7773929797</v>
       </c>
       <c r="H52" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -1951,6 +2041,12 @@
       <c r="E57" t="s">
         <v>95</v>
       </c>
+      <c r="G57" s="3">
+        <v>2049572580</v>
+      </c>
+      <c r="H57" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
@@ -1985,6 +2081,9 @@
       <c r="E59" t="s">
         <v>95</v>
       </c>
+      <c r="G59" s="3">
+        <v>5527953290</v>
+      </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
@@ -2080,7 +2179,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
         <v>90</v>
       </c>
@@ -2096,8 +2195,14 @@
       <c r="E65" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="G65" s="3">
+        <v>6639477377</v>
+      </c>
+      <c r="H65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
         <v>93</v>
       </c>

--- a/HOSPITALITY MEMBERS.xlsx
+++ b/HOSPITALITY MEMBERS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/341706f11dbb6ad1/Documents/Protocol Bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{B8933D2A-CF6E-47BB-B1FC-6E30EEB082BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF83D1CF-B224-476B-9B87-37EDF33BBBA7}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{B8933D2A-CF6E-47BB-B1FC-6E30EEB082BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B44FD61-B591-4864-9B89-F54EB72FA5D0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{4C2305D9-A961-4A00-AA72-500382EFDABF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="160">
   <si>
     <t>NAME</t>
   </si>
@@ -505,6 +505,15 @@
   </si>
   <si>
     <t>@Joyifeee</t>
+  </si>
+  <si>
+    <t>@chubionoja</t>
+  </si>
+  <si>
+    <t>@Onyinye49</t>
+  </si>
+  <si>
+    <t>@Ela033298</t>
   </si>
 </sst>
 </file>
@@ -1555,6 +1564,12 @@
       <c r="E30" t="s">
         <v>98</v>
       </c>
+      <c r="G30" s="3">
+        <v>6534789056</v>
+      </c>
+      <c r="H30" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
@@ -1708,6 +1723,12 @@
       <c r="E39" t="s">
         <v>92</v>
       </c>
+      <c r="G39" s="3">
+        <v>6179135655</v>
+      </c>
+      <c r="H39" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" t="s">
@@ -2217,6 +2238,12 @@
       </c>
       <c r="E66" t="s">
         <v>92</v>
+      </c>
+      <c r="G66" s="3">
+        <v>6462616674</v>
+      </c>
+      <c r="H66" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/HOSPITALITY MEMBERS.xlsx
+++ b/HOSPITALITY MEMBERS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/341706f11dbb6ad1/Documents/Protocol Bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{B8933D2A-CF6E-47BB-B1FC-6E30EEB082BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B44FD61-B591-4864-9B89-F54EB72FA5D0}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{B8933D2A-CF6E-47BB-B1FC-6E30EEB082BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{470AE4AC-AD72-4E9A-A1C5-5C4D6EF3CFFA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{4C2305D9-A961-4A00-AA72-500382EFDABF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="167">
   <si>
     <t>NAME</t>
   </si>
@@ -514,6 +514,27 @@
   </si>
   <si>
     <t>@Ela033298</t>
+  </si>
+  <si>
+    <t>@Ayanok_j1</t>
+  </si>
+  <si>
+    <t>@timothy</t>
+  </si>
+  <si>
+    <t>@mosope</t>
+  </si>
+  <si>
+    <t>Nimo💕</t>
+  </si>
+  <si>
+    <t>Fufilment</t>
+  </si>
+  <si>
+    <t>@iiamodun</t>
+  </si>
+  <si>
+    <t>Moyin</t>
   </si>
 </sst>
 </file>
@@ -1356,6 +1377,12 @@
       <c r="F19" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="G19" s="3">
+        <v>5519077885</v>
+      </c>
+      <c r="H19" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" t="s">
@@ -1587,6 +1614,12 @@
       <c r="E31" t="s">
         <v>98</v>
       </c>
+      <c r="G31" s="3">
+        <v>7057518823</v>
+      </c>
+      <c r="H31" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" t="s">
@@ -1689,6 +1722,12 @@
       <c r="E37" t="s">
         <v>91</v>
       </c>
+      <c r="G37" s="3">
+        <v>6142508782</v>
+      </c>
+      <c r="H37" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" t="s">
@@ -1746,6 +1785,12 @@
       <c r="E40" t="s">
         <v>95</v>
       </c>
+      <c r="G40" s="3">
+        <v>5303079660</v>
+      </c>
+      <c r="H40" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
@@ -1766,6 +1811,9 @@
       <c r="G41" s="3">
         <v>1235638602</v>
       </c>
+      <c r="H41" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" t="s">
@@ -1823,6 +1871,12 @@
       <c r="E44" t="s">
         <v>100</v>
       </c>
+      <c r="G44" s="3">
+        <v>5530809050</v>
+      </c>
+      <c r="H44" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" t="s">
@@ -2027,6 +2081,12 @@
       </c>
       <c r="E55" t="s">
         <v>98</v>
+      </c>
+      <c r="G55" s="3">
+        <v>5745452026</v>
+      </c>
+      <c r="H55" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="56" spans="1:8">
